--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.04319811408235139</v>
       </c>
       <c r="C2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>34644449</v>
+        <v>3866334</v>
       </c>
       <c r="L2" t="n">
-        <v>19807761</v>
+        <v>1944912</v>
       </c>
       <c r="M2" t="n">
-        <v>5075356</v>
+        <v>444795</v>
       </c>
       <c r="N2" t="n">
-        <v>289161</v>
+        <v>18784</v>
       </c>
       <c r="O2" t="n">
-        <v>3035712</v>
+        <v>281945</v>
       </c>
       <c r="P2" t="n">
-        <v>1242987</v>
+        <v>123126</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999173879623413</v>
+        <v>0.9998226761817932</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8796097636222839</v>
+        <v>0.7852599024772644</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7674541473388672</v>
+        <v>0.6028633713722229</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6793197989463806</v>
+        <v>0.4764233231544495</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5030128955841064</v>
+        <v>0.2625957727432251</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7463279366493225</v>
+        <v>0.554776132106781</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8032547831535339</v>
+        <v>0.636616051197052</v>
       </c>
       <c r="X2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>49702176</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>33605581</v>
+        <v>3785410</v>
       </c>
       <c r="AG2" t="n">
-        <v>18356699</v>
+        <v>1840830</v>
       </c>
       <c r="AH2" t="n">
-        <v>4567221</v>
+        <v>412538</v>
       </c>
       <c r="AI2" t="n">
-        <v>256703</v>
+        <v>17472</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2789418</v>
+        <v>262478</v>
       </c>
       <c r="AK2" t="n">
-        <v>1165812</v>
+        <v>115591</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.85073322057724</v>
+        <v>0.7666283845901489</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7161439061164856</v>
+        <v>0.5745255947113037</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6164535880088806</v>
+        <v>0.4454534351825714</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3630753755569458</v>
+        <v>0.197696253657341</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6862995624542236</v>
+        <v>0.5166340470314026</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7540320754051208</v>
+        <v>0.5981020927429199</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01237542759378918</v>
       </c>
       <c r="C3" t="n">
-        <v>1329</v>
+        <v>419</v>
       </c>
       <c r="D3" t="n">
-        <v>34644449</v>
+        <v>3866334</v>
       </c>
       <c r="E3" t="n">
-        <v>4240362</v>
+        <v>913166</v>
       </c>
       <c r="F3" t="n">
-        <v>248590</v>
+        <v>64948</v>
       </c>
       <c r="G3" t="n">
-        <v>38896</v>
+        <v>7960</v>
       </c>
       <c r="H3" t="n">
-        <v>11480</v>
+        <v>4619</v>
       </c>
       <c r="I3" t="n">
-        <v>1872</v>
+        <v>693</v>
       </c>
       <c r="J3" t="n">
-        <v>78856917</v>
+        <v>9856526</v>
       </c>
       <c r="K3" t="n">
-        <v>84634512</v>
+        <v>10154959</v>
       </c>
       <c r="L3" t="n">
-        <v>96669544</v>
+        <v>11519163</v>
       </c>
       <c r="M3" t="n">
-        <v>118717394</v>
+        <v>14645429</v>
       </c>
       <c r="N3" t="n">
-        <v>127567493</v>
+        <v>15928533</v>
       </c>
       <c r="O3" t="n">
-        <v>123456115</v>
+        <v>15333529</v>
       </c>
       <c r="P3" t="n">
-        <v>126711627</v>
+        <v>15806529</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8840806484222412</v>
+        <v>0.795846700668335</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7650230526924133</v>
+        <v>0.5947697758674622</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6812622547149658</v>
+        <v>0.4751306772232056</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4072632789611816</v>
+        <v>0.2107743620872498</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7449113726615906</v>
+        <v>0.5521815419197083</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8034188747406006</v>
+        <v>0.6360142827033997</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33605581</v>
+        <v>3785410</v>
       </c>
       <c r="Z3" t="n">
-        <v>5154314</v>
+        <v>974604</v>
       </c>
       <c r="AA3" t="n">
-        <v>296426</v>
+        <v>72569</v>
       </c>
       <c r="AB3" t="n">
-        <v>110696</v>
+        <v>18171</v>
       </c>
       <c r="AC3" t="n">
-        <v>17504</v>
+        <v>6383</v>
       </c>
       <c r="AD3" t="n">
-        <v>2457</v>
+        <v>1002</v>
       </c>
       <c r="AE3" t="n">
-        <v>78861024</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>83479899</v>
+        <v>10059933</v>
       </c>
       <c r="AG3" t="n">
-        <v>95395485</v>
+        <v>11437118</v>
       </c>
       <c r="AH3" t="n">
-        <v>118271627</v>
+        <v>14620677</v>
       </c>
       <c r="AI3" t="n">
-        <v>127402869</v>
+        <v>15910375</v>
       </c>
       <c r="AJ3" t="n">
-        <v>123212920</v>
+        <v>15314222</v>
       </c>
       <c r="AK3" t="n">
-        <v>126635786</v>
+        <v>15799138</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8575701117515564</v>
+        <v>0.7791892886161804</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7089795470237732</v>
+        <v>0.5629406571388245</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6130555868148804</v>
+        <v>0.4406736791133881</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3615484237670898</v>
+        <v>0.1960524618625641</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6844750642776489</v>
+        <v>0.5140559673309326</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7535359263420105</v>
+        <v>0.5970917940139771</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.09026265231825138</v>
       </c>
       <c r="C4" t="n">
-        <v>595</v>
+        <v>169</v>
       </c>
       <c r="D4" t="n">
-        <v>4458148</v>
+        <v>981136</v>
       </c>
       <c r="E4" t="n">
-        <v>19807761</v>
+        <v>1944912</v>
       </c>
       <c r="F4" t="n">
-        <v>1394994</v>
+        <v>277672</v>
       </c>
       <c r="G4" t="n">
-        <v>56357</v>
+        <v>12836</v>
       </c>
       <c r="H4" t="n">
-        <v>154469</v>
+        <v>46442</v>
       </c>
       <c r="I4" t="n">
-        <v>19394</v>
+        <v>6858</v>
       </c>
       <c r="J4" t="n">
-        <v>4107</v>
+        <v>1102</v>
       </c>
       <c r="K4" t="n">
-        <v>4741710</v>
+        <v>1057302</v>
       </c>
       <c r="L4" t="n">
-        <v>6001938</v>
+        <v>1281212</v>
       </c>
       <c r="M4" t="n">
-        <v>2395876</v>
+        <v>488818</v>
       </c>
       <c r="N4" t="n">
-        <v>285697</v>
+        <v>52748</v>
       </c>
       <c r="O4" t="n">
-        <v>1031819</v>
+        <v>226269</v>
       </c>
       <c r="P4" t="n">
-        <v>304451</v>
+        <v>70281</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999586939811707</v>
+        <v>0.999911367893219</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8818394541740417</v>
+        <v>0.7905178070068359</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7662367224693298</v>
+        <v>0.5987892150878906</v>
       </c>
       <c r="T4" t="n">
-        <v>0.680289626121521</v>
+        <v>0.4757761061191559</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4501022398471832</v>
+        <v>0.2338485270738602</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7456189393997192</v>
+        <v>0.5534757971763611</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8033367991447449</v>
+        <v>0.6363150477409363</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>5517596</v>
+        <v>1058017</v>
       </c>
       <c r="Z4" t="n">
-        <v>18356699</v>
+        <v>1840830</v>
       </c>
       <c r="AA4" t="n">
-        <v>1669513</v>
+        <v>287515</v>
       </c>
       <c r="AB4" t="n">
-        <v>110467</v>
+        <v>19661</v>
       </c>
       <c r="AC4" t="n">
-        <v>209499</v>
+        <v>55234</v>
       </c>
       <c r="AD4" t="n">
-        <v>27944</v>
+        <v>8768</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>5896323</v>
+        <v>1152328</v>
       </c>
       <c r="AG4" t="n">
-        <v>7275997</v>
+        <v>1363257</v>
       </c>
       <c r="AH4" t="n">
-        <v>2841643</v>
+        <v>513570</v>
       </c>
       <c r="AI4" t="n">
-        <v>450321</v>
+        <v>70906</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1275014</v>
+        <v>245576</v>
       </c>
       <c r="AK4" t="n">
-        <v>380292</v>
+        <v>77672</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8541379570960999</v>
+        <v>0.7728578448295593</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7125437259674072</v>
+        <v>0.5686741471290588</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6147499680519104</v>
+        <v>0.4430506527423859</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3623103201389313</v>
+        <v>0.1968709379434586</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6853861212730408</v>
+        <v>0.5153418183326721</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7537839412689209</v>
+        <v>0.5975965261459351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>669</v>
+        <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>190785</v>
+        <v>55493</v>
       </c>
       <c r="E5" t="n">
-        <v>1477545</v>
+        <v>290437</v>
       </c>
       <c r="F5" t="n">
-        <v>5075356</v>
+        <v>444795</v>
       </c>
       <c r="G5" t="n">
-        <v>104406</v>
+        <v>17596</v>
       </c>
       <c r="H5" t="n">
-        <v>541124</v>
+        <v>110438</v>
       </c>
       <c r="I5" t="n">
-        <v>60045</v>
+        <v>17199</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4542529</v>
+        <v>991805</v>
       </c>
       <c r="L5" t="n">
-        <v>6083957</v>
+        <v>1325113</v>
       </c>
       <c r="M5" t="n">
-        <v>2374574</v>
+        <v>491358</v>
       </c>
       <c r="N5" t="n">
-        <v>420849</v>
+        <v>70335</v>
       </c>
       <c r="O5" t="n">
-        <v>1039554</v>
+        <v>228657</v>
       </c>
       <c r="P5" t="n">
-        <v>304135</v>
+        <v>70464</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999680519104004</v>
+        <v>0.9999314546585083</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9277846217155457</v>
+        <v>0.8724918365478516</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9059925675392151</v>
+        <v>0.8378182649612427</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9628941416740417</v>
+        <v>0.9390073418617249</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9945042729377747</v>
+        <v>0.9923410415649414</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9838882684707642</v>
+        <v>0.9716916680335999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9952662587165833</v>
+        <v>0.991241991519928</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>260643</v>
+        <v>69548</v>
       </c>
       <c r="Z5" t="n">
-        <v>1757599</v>
+        <v>299719</v>
       </c>
       <c r="AA5" t="n">
-        <v>4567221</v>
+        <v>412538</v>
       </c>
       <c r="AB5" t="n">
-        <v>128521</v>
+        <v>18569</v>
       </c>
       <c r="AC5" t="n">
-        <v>656535</v>
+        <v>116001</v>
       </c>
       <c r="AD5" t="n">
-        <v>79411</v>
+        <v>19778</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>5581397</v>
+        <v>1072729</v>
       </c>
       <c r="AG5" t="n">
-        <v>7535019</v>
+        <v>1429195</v>
       </c>
       <c r="AH5" t="n">
-        <v>2882709</v>
+        <v>523615</v>
       </c>
       <c r="AI5" t="n">
-        <v>453307</v>
+        <v>71647</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1285848</v>
+        <v>248124</v>
       </c>
       <c r="AK5" t="n">
-        <v>381310</v>
+        <v>77999</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9107231497764587</v>
+        <v>0.8615431189537048</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8847958445549011</v>
+        <v>0.8262363076210022</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9554744362831116</v>
+        <v>0.9354599118232727</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9929713606834412</v>
+        <v>0.991129457950592</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9800809025764465</v>
+        <v>0.9692789316177368</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9940760731697083</v>
+        <v>0.9903131723403931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1018</v>
+        <v>225</v>
       </c>
       <c r="D6" t="n">
-        <v>82800</v>
+        <v>15464</v>
       </c>
       <c r="E6" t="n">
-        <v>103757</v>
+        <v>20365</v>
       </c>
       <c r="F6" t="n">
-        <v>145719</v>
+        <v>19097</v>
       </c>
       <c r="G6" t="n">
-        <v>289161</v>
+        <v>18784</v>
       </c>
       <c r="H6" t="n">
-        <v>75644</v>
+        <v>12526</v>
       </c>
       <c r="I6" t="n">
-        <v>11911</v>
+        <v>2658</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>99647</v>
+        <v>16519</v>
       </c>
       <c r="Z6" t="n">
-        <v>116686</v>
+        <v>21042</v>
       </c>
       <c r="AA6" t="n">
-        <v>134966</v>
+        <v>18533</v>
       </c>
       <c r="AB6" t="n">
-        <v>256703</v>
+        <v>17472</v>
       </c>
       <c r="AC6" t="n">
-        <v>87764</v>
+        <v>12698</v>
       </c>
       <c r="AD6" t="n">
-        <v>14244</v>
+        <v>2855</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>9622</v>
+        <v>5110</v>
       </c>
       <c r="E7" t="n">
-        <v>167146</v>
+        <v>52062</v>
       </c>
       <c r="F7" t="n">
-        <v>573335</v>
+        <v>116418</v>
       </c>
       <c r="G7" t="n">
-        <v>77895</v>
+        <v>12133</v>
       </c>
       <c r="H7" t="n">
-        <v>3035712</v>
+        <v>281945</v>
       </c>
       <c r="I7" t="n">
-        <v>211229</v>
+        <v>42873</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>17739</v>
+        <v>7990</v>
       </c>
       <c r="Z7" t="n">
-        <v>227580</v>
+        <v>61043</v>
       </c>
       <c r="AA7" t="n">
-        <v>694428</v>
+        <v>121849</v>
       </c>
       <c r="AB7" t="n">
-        <v>89865</v>
+        <v>11973</v>
       </c>
       <c r="AC7" t="n">
-        <v>2789418</v>
+        <v>262478</v>
       </c>
       <c r="AD7" t="n">
-        <v>256236</v>
+        <v>45269</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>99</v>
       </c>
       <c r="E8" t="n">
-        <v>13128</v>
+        <v>5182</v>
       </c>
       <c r="F8" t="n">
-        <v>33238</v>
+        <v>10683</v>
       </c>
       <c r="G8" t="n">
-        <v>8143</v>
+        <v>2223</v>
       </c>
       <c r="H8" t="n">
-        <v>249102</v>
+        <v>52244</v>
       </c>
       <c r="I8" t="n">
-        <v>1242987</v>
+        <v>123126</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>698</v>
+        <v>254</v>
       </c>
       <c r="Z8" t="n">
-        <v>19818</v>
+        <v>6849</v>
       </c>
       <c r="AA8" t="n">
-        <v>46310</v>
+        <v>13104</v>
       </c>
       <c r="AB8" t="n">
-        <v>10772</v>
+        <v>2532</v>
       </c>
       <c r="AC8" t="n">
-        <v>303712</v>
+        <v>55260</v>
       </c>
       <c r="AD8" t="n">
-        <v>1165812</v>
+        <v>115591</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
